--- a/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_01_22_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_01_22_Cau.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1206,7 +1206,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định path cần ghi và user sở hữu nó trước khi chuyển sang `USER`.</t>
+          <t>Để tiến trình chạy dưới user non-root (`USER 10001`) có thể ghi vào thư mục `/app/tmp`, Dockerfile cần gán quyền sở hữu hoặc quyền ghi tối thiểu cho thư mục đó trước khi chuyển sang lệnh `USER`.</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1254,7 +1254,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt file bị Git bỏ qua với file Docker vẫn gửi trong build context.</t>
+          <t>Docker build context gửi tất cả các tệp trong thư mục trừ khi được chỉ định rõ trong `.dockerignore`; tệp `.gitignore` không có tác dụng với Docker daemon khi build image.</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1309,7 +1309,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định finding nằm trong final image nào, package còn reachable lúc chạy không và bằng chứng còn hiệu lực đến khi nào.</t>
+          <t>Để quyết định phát hành D1 khi builder stage có CVE: Cần (a) image digest bất biến D1 đã qua quét, (b) SBOM của final image để chứng minh package lỗi không tồn tại hoặc không reachable ở runtime, (c) đánh giá mức độ, bản vá và exception owner có thời hạn.</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1357,7 +1357,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trong Compose hãy gọi tên service; readiness là khả năng phục vụ, không chỉ process đã start.</t>
+          <t>Trong Docker Compose, các service độc lập giao tiếp qua mạng nội bộ bằng tên service DNS và cần khai báo điều kiện phụ thuộc trạng thái sẵn sàng (healthcheck/readiness), không gọi `localhost`.</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu thời lượng tác vụ với timeout, rồi kiểm tra cách lấy kết quả sau khi submit.</t>
+          <t>Khi tác vụ xử lý kéo dài 90s vượt quá thời gian timeout 30s của HTTP gateway, giải pháp kiến trúc chuẩn là chuyển sang mô hình Async Job (HTTP 202 Accepted) kèm `job_id` và endpoint tra cứu trạng thái/kết quả.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1507,7 +1507,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt first-byte latency với tổng compute.</t>
+          <t>Server-Sent Events (SSE) streaming giúp giảm độ trễ của token đầu tiên (Time-to-First-Token - TTFT) để cải thiện trải nghiệm người dùng, nhưng không làm giảm tổng khối lượng tính toán của mô hình.</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1555,7 +1555,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm ranh giới intermediary: byte có được đẩy ra sớm, connection có được giữ sống và event có thể resume không.</t>
+          <t>Khi streaming SSE bị proxy gom buffer, giải pháp vận hành là tắt cơ chế buffering trên reverse proxy (`proxy_buffering off`), ép flush sớm và bổ sung heartbeat/event ID để duy trì kết nối.</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1706,7 +1706,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đặt tenant/user vào key trước khi xét TTL hay cách lưu message.</t>
+          <t>Trong hệ thống multi-tenant, khóa lưu trữ trạng thái phiên bắt buộc phải được đặt phạm vi (namespaced/scoped) theo `tenant_id` (ví dụ `tenant:{id}:conversation:{id}`) để ngăn chặn rò rỉ dữ liệu chéo giữa các tổ chức.</t>
         </is>
       </c>
     </row>
